--- a/DiffReturns.xlsx
+++ b/DiffReturns.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11211"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10908"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marianatrujillo/Desktop/Do nothing, better?/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marianatrujillo/Desktop/PassiveFundsOverHarvard-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC93E806-6429-B34C-B5B4-26FCCC66BB9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36AC06C0-87DE-1B49-B8FA-8EC622A74CB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="1000" windowWidth="27640" windowHeight="16440" xr2:uid="{6FA3DB06-81F6-CA40-9BC9-1ECA7827134E}"/>
   </bookViews>
@@ -44,13 +44,13 @@
     <t>Harvard</t>
   </si>
   <si>
-    <t>Montgomery County</t>
+    <t>Nevada_PERS</t>
   </si>
   <si>
-    <t>Butler County</t>
+    <t>Montgomery_County</t>
   </si>
   <si>
-    <t>Nevada PERS</t>
+    <t>Butler_County</t>
   </si>
 </sst>
 </file>
@@ -93,10 +93,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -115,9 +117,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2013 - 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -155,7 +157,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -261,7 +263,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -403,7 +405,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -411,7 +413,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7502CA99-9CC2-494C-BB1F-38B239C0206C}">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
@@ -419,13 +421,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
         <v>4</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
       </c>
       <c r="E1" t="s">
         <v>1</v>
@@ -435,16 +437,16 @@
       <c r="A2" s="1">
         <v>2013</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="3">
         <v>0.124</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="3">
         <v>0.1008</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="3">
         <v>0.13500000000000001</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="3">
         <v>0.113</v>
       </c>
       <c r="F2" s="2"/>
@@ -453,16 +455,16 @@
       <c r="A3" s="1">
         <v>2014</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="3">
         <v>0.17599999999999999</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="3">
         <v>0.16189999999999999</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="3">
         <v>0.17299999999999999</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="3">
         <v>0.154</v>
       </c>
       <c r="F3" s="2"/>
@@ -471,16 +473,16 @@
       <c r="A4" s="1">
         <v>2015</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="3">
         <v>4.1799999999999997E-2</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="3">
         <v>8.0500000000000002E-2</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="3">
         <v>8.4000000000000005E-2</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="3">
         <v>5.8000000000000003E-2</v>
       </c>
       <c r="F4" s="2"/>
@@ -489,16 +491,16 @@
       <c r="A5" s="1">
         <v>2016</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="3">
         <v>2.2700000000000001E-2</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="3">
         <v>3.5000000000000001E-3</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="3">
         <v>-7.0000000000000001E-3</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="3">
         <v>-0.02</v>
       </c>
       <c r="F5" s="2"/>
@@ -507,16 +509,16 @@
       <c r="A6" s="1">
         <v>2017</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="3">
         <v>0.11840000000000001</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="3">
         <v>7.6899999999999996E-2</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="3">
         <v>8.5999999999999993E-2</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="3">
         <v>8.1000000000000003E-2</v>
       </c>
       <c r="F6" s="2"/>
@@ -525,16 +527,16 @@
       <c r="A7" s="1">
         <v>2018</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="3">
         <v>8.5400000000000004E-2</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="3">
         <v>0.1464</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="3">
         <v>0.13700000000000001</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="3">
         <v>0.1</v>
       </c>
       <c r="F7" s="2"/>
@@ -543,16 +545,16 @@
       <c r="A8" s="1">
         <v>2019</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="3">
         <v>8.4500000000000006E-2</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="3">
         <v>-5.4199999999999998E-2</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="3">
         <v>-5.7000000000000002E-2</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="3">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="F8" s="2"/>
@@ -561,16 +563,16 @@
       <c r="A9" s="1">
         <v>2020</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="3">
         <v>7.1499999999999994E-2</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="3">
         <v>0.20230000000000001</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="3">
         <v>0.20100000000000001</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="3">
         <v>7.2999999999999995E-2</v>
       </c>
       <c r="F9" s="2"/>
@@ -579,16 +581,16 @@
       <c r="A10" s="1">
         <v>2021</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="3">
         <v>0.27250000000000002</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="3">
         <v>0.12620000000000001</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="3">
         <v>9.6000000000000002E-2</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="3">
         <v>0.33600000000000002</v>
       </c>
       <c r="F10" s="2"/>
@@ -597,16 +599,16 @@
       <c r="A11" s="1">
         <v>2022</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="3">
         <v>-5.0700000000000002E-2</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="3">
         <v>0.12470000000000001</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="3">
         <v>0.13900000000000001</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="3">
         <v>-1.7999999999999999E-2</v>
       </c>
       <c r="F11" s="2"/>
@@ -615,17 +617,23 @@
       <c r="A12" s="1">
         <v>2023</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="3">
         <v>9.2999999999999999E-2</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="3">
         <v>-0.16020000000000001</v>
       </c>
-      <c r="D12" s="1"/>
-      <c r="E12" s="2">
+      <c r="D12" s="3"/>
+      <c r="E12" s="3">
         <v>2.9000000000000001E-2</v>
       </c>
       <c r="F12" s="2"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
